--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0099.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0099.xlsx
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Nhanh lên! Dự án Công cụ hóa Nhiên liệu F.U.E.L.!</t>
+          <t>Tăng tốc nào! Dự án Công Cụ Hóa Nhiên Liệu F.U.E.L.!</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Squeezy Jelly</t>
+          <t>Thạch Nén Nhũ</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4844,7 +4844,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Rainbow Squeezy Jelly</t>
+          <t>Thạch Ép Cầu Vồng</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4914,7 +4914,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Instant Wakeup Energy Gel Sachet</t>
+          <t>Gói Gel Năng Lượng Tỉnh Táo Tức Thì</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Savory Super Star</t>
+          <t>Siêu Sao Đậm Đà</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>"Ăn thêm 5 giây nữa"</t>
+          <t>"Nhai Thêm 5 Giây Nữa"</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Munchie Madness Mode</t>
+          <t>Chế Độ Điên Cuồng Nhai Nhét</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Mornye</t>
+          <t>Chàooo</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Hiện Chưa Mở</t>
+          <t>Chưa mở</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Unmarked</t>
+          <t>Không đánh dấu</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Batch Discard</t>
+          <t>Hủy Hàng Loạt</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Batch Undiscard</t>
+          <t>Hoàn Tác Bỏ Hàng Loạt</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Batch Lock</t>
+          <t>Khóa Hàng Loạt</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Batch Unlock</t>
+          <t>Mở Khóa Hàng Loạt</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Batch Discard Confirmation</t>
+          <t>Xác Nhận Hủy Hàng Loạt</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Batch Undiscard Confirmation</t>
+          <t>Xác Nhận Hoàn Tác Bỏ Hàng Loạt</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Batch Lock Confirmation</t>
+          <t>Xác Nhận Khóa Hàng Loạt</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Batch Unlock Confirmation</t>
+          <t>Xác Nhận Mở Khóa Hàng Loạt</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Sonata Effect Filter:</t>
+          <t>Bộ Lọc Hiệu Ứng Sonata:</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Không có Echo nào được đánh dấu "Loại bỏ"</t>
+          <t>Không có Echo nào được đánh dấu "Loại bỏ".</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Loại bỏ Echo thành công</t>
+          <t>Đã loại bỏ Echo thành công</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Nhận Spindrift</t>
+          <t>Nhận Hoa Sương Biển</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Aerial Tactics</t>
+          <t>Chiến Thuật Trên Không</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Charged Leap</t>
+          <t>Nhảy Tấn Công đã nạp</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Mở khóa Charged Leap</t>
+          <t>Mở khóa Nhảy Tích Năng</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Energy Recycle</t>
+          <t>Tái Chế Năng Lượng</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 3 Điểm Điều Chỉnh Hàng Không</t>
+          <t>Nhận tổng cộng 3 Điểm Nâng Cấp Hàng Không.</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Efficient Propulsion</t>
+          <t>Động Lực Hiệu Quả</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 6 Điểm Điều Chỉnh Hàng Không</t>
+          <t>Thu thập tổng cộng 6 Điểm Nâng Cấp Hàng Không</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Low Kéo Design</t>
+          <t>Thiết Kế Khí Động Học Thấp</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 10 Điểm Điều Chỉnh Hàng Không</t>
+          <t>Thu thập tổng cộng 10 Điểm Cải Tạo Hàng Không</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Steelwing Comet</t>
+          <t>Sao Chổi Cánh Thép</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Void Storm: Additional Supply</t>
+          <t>Bão Hư Không: Hỗ trợ bổ sung</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Void Storm: Enhanced Resonance</t>
+          <t>Bão Hư Không: Cộng Hưởng Tăng Cường</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Life Hỗ Trợ Mô-đun</t>
+          <t>Mô-đun Hỗ Trợ Sinh Tồn</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Assault Tech: Emergency Loadout</t>
+          <t>Trang bị Khẩn cấp: Công Nghệ Tấn Công</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Enhanced Resonance</t>
+          <t>Cộng Hưởng Cường Hóa</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Assault Tech: Annihilation Mode</t>
+          <t>Công Nghệ Tấn Công: Chế Độ Tiêu Diệt</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Vui lòng tiếp tục Nhiệm Vụ Chính Chương III</t>
+          <t>Hãy tiếp tục Nhiệm Vụ Chính Chương III</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Đạt 10.000 điểm trong Stability Accords để mở khóa</t>
+          <t>Đạt 10.000 điểm trong Hiệp Ước Ổn Định để mở khóa</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Tổng điểm</t>
+          <t>Tổng Điểm</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Remaining Bosses</t>
+          <t>Boss còn lại</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Không Record</t>
+          <t>Không có bản ghi</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Vòng Luân Hồi Ngày Tận Thế</t>
+          <t>Vòng Luân Tận Thế</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Hiệp ước Ổn định</t>
+          <t>Hiệp Ước Ổn Định</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Singularity Expansion</t>
+          <t>Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Encrypted Data Obtained</t>
+          <t>Đã Nhận Dữ Liệu Mã Hóa</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Chưa có dữ liệu</t>
+          <t>Chưa có bản ghi nào</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Power Circuit</t>
+          <t>Mạch Năng Lượng</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Hoàn thành Septimont 4 trong "Star Bouncing"</t>
+          <t>Hoàn thành Septimont 4 trong "Nhảy Sao"</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Hoàn thành SkyArk 4 trong "Star Bouncing"</t>
+          <t>Hoàn thành SkyArk 4 trong "Nhảy Sao"</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 4.000 điểm trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
+          <t>Đạt tổng 4.000 điểm trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 6.000 điểm trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
+          <t>Đạt tổng cộng 6.000 điểm trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Đạt 10.000 điểm trong Stability Accords trong "Doubled Pawns Matrix"</t>
+          <t>Đạt 10.000 điểm trong Hiệp Ước Ổn Định ở "Ma Trận Tốt Đôi"</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Mở khóa Mô-đun Chiến Thuật Hàng Không Xe Máy Thám Hiểm</t>
+          <t>Mở khóa Mô-đun Chiến Thuật Trên Không cho Xe Thám Hiểm</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính "Starlights from Yesterdays"</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Ánh Sao Từ Những Ngày Xưa"</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Hoàn thành Segue "Beneath a Melting Night Sky"</t>
+          <t>Hoàn thành Đoạn Chuyển "Beneath a Melting Night Sky"</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "A Perfect Ngày for Flying"</t>
+          <t>Hoàn thành Nhiệm Vụ Thám Hiểm "Một Ngày Tuyệt Vời Để Bay Lượn"</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Đạt 25% Tiến Độ Thám Hiểm tại 2 khu vực của Dimmr Plains</t>
+          <t>Đạt 25% Tiến Độ Thám Hiểm ở 2 khu vực thuộc Dimmr Plains</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Đạt 50% Tiến Độ Thám Hiểm tại 4 khu vực của Dimmr Plains</t>
+          <t>Hoàn thành 50% Tiến Độ Thám Hiểm ở 4 khu vực thuộc Dimmr Plains</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Đạt tổng cộng 1.000 Activity Points</t>
+          <t>Đạt tổng cộng 1.000 Điểm Hoạt Động</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Invert Vehicle Gliding Vertical Input</t>
+          <t>Đảo Ngược Điều Khiển Dọc Khi Lướt Bay</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Anisotropic Filtering</t>
+          <t>Lọc Bất Đẳng Hướng</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Tăng cường độ sâu môi trường bằng cách thêm bóng ở các góc và khe hẹp</t>
+          <t>Tăng cường chiều sâu môi trường bằng cách bổ sung bóng đổ ở các góc khuất và khe hẹp</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Mô phỏng bụi và sương mù trong không khí để tạo hiệu ứng chân thực</t>
+          <t>Mô phỏng bụi và sương mù bay lơ lửng để tạo hiệu ứng chân thực</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Mô phỏng các tia sáng chân thực</t>
+          <t>Mô phỏng hiệu ứng tia sáng chân thực</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Tạo hiệu ứng phát sáng cho các nguồn sáng mạnh để tăng tính khí quyển</t>
+          <t>Khiến ánh sáng rực rỡ phát sáng để tạo không khí lung linh</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Kích hoạt mô phỏng vật lý cho một số trang phục và phụ kiện tóc của nhân vật</t>
+          <t>Kích hoạt mô phỏng vật lý cho một số phụ kiện quần áo và tóc của nhân vật</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Mô phỏng cách mắt điều chỉnh khi di chuyển giữa không gian tối và sáng</t>
+          <t>Mô phỏng sự điều tiết của mắt khi di chuyển giữa không gian tối và sáng</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Mô phỏng sự lan truyền và phản chiếu ánh sáng tự nhiên để tạo hiệu ứng ánh sáng chân thực</t>
+          <t>Mô phỏng lan truyền và phản chiếu ánh sáng tự nhiên để tạo hiệu ứng chiếu sáng chân thực</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Kích hoạt phản chiếu động trên mặt nước, kính và bề mặt kim loại để tạo hiệu ứng chân thực</t>
+          <t>Tạo phản chiếu động trên nước, kính và bề mặt kim loại để mang lại hiệu ứng chân thực</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Kích hoạt phản xạ ánh sáng chân thực để tạo sự chuyển màu tự nhiên hơn</t>
+          <t>Kích hoạt phản xạ ánh sáng chân thực để chuyển màu tự nhiên hơn</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Làm mềm bóng dựa trên khoảng cách nguồn sáng để tạo hiệu ứng ánh sáng chân thực</t>
+          <t>Làm mềm bóng đổ dựa trên khoảng cách nguồn sáng để tạo hiệu ứng ánh sáng chân thực</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Enabled</t>
+          <t>Đã bật</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Disabled</t>
+          <t>Đã vô hiệu hóa</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Hiệp ước Ổn định</t>
+          <t>Hiệp Ước Ổn Định</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Singularity Expansion</t>
+          <t>Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Build</t>
+          <t>Xây Dựng</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Class</t>
+          <t>Hạng</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Tactical ROM Quality</t>
+          <t>Chất lượng ROM Chiến Thuật</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Không thể thay đổi đội hình Trial Pinball</t>
+          <t>Không thể thay đổi đội hình Pinball Thử Nghiệm</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Chưa triển khai Pinball nào</t>
+          <t>Chưa triển khai Bóng Bi-a nào</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Cast Pearls Before Swine</t>
+          <t>Ném Ngọc Trước Heo</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>An Ending Không One Knows</t>
+          <t>Một Kết Thúc Mà Không Ai Biết</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Đó Là Một Con Bắt Chước?!</t>
+          <t>Nó Là Kẻ Bắt Chước Sao?!</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Tất cả Shapes of Light</t>
+          <t>Mọi sắc thái của Ánh Sáng</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Dimmr Plains Void Storm Trooper Type I</t>
+          <t>Lính Bão Hư Không Loại I - Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Dimmr Plains Void Storm Trooper Type II</t>
+          <t>Lính Bão Hư Không Đồng Bằng Dimmr Loại II</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Dimmr Plains Void Storm Trooper Type III</t>
+          <t>Lính Bão Hư Không Đồng Bằng Dimmr Loại III</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Dimmr Plains Void Storm Trooper Type IV</t>
+          <t>Lính Bão Hư Không Đồng Bằng Dimmr Loại IV</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Dimmr Plains Tất cả-Terrain Void Storm Trooper</t>
+          <t>Lính Bão Hư Không Đa Địa Hình - Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Made in Abyss</t>
+          <t>Sản xuất tại Vực Sâu</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>The Answer Sought</t>
+          <t>Câu Trả Lời Được Tìm Kiếm</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12474,7 +12474,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>I'm Fired Up</t>
+          <t>Tôi là Fired Up.</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Tìm Thấy Bọn TARD-Es</t>
+          <t>Tìm thấy Ngươi rồi, TARD-Es!</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Land Aviator</t>
+          <t>Phi Hành Gia Mặt Đất</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Kill Screen</t>
+          <t>Tiêu Diệt Màn Hình</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>A Small Wish</t>
+          <t>Một Điều Ước Nhỏ</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>The Thật sự Star</t>
+          <t>Ngôi Sao Chân Thật</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Vùng Xa Xôi của Aurora</t>
+          <t>Viễn Xứ Aurora</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Our Sun</t>
+          <t>Mặt Trời của chúng ta</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Bỏ Túi Trong Một Phát</t>
+          <t>Một Phát Trúng Tủ</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Hear Once More</t>
+          <t>Nghe lại lần nữa</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>And I'm Home</t>
+          <t>Và ta là Home.</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>The Past Within</t>
+          <t>Quá Khứ Bên Trong</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>The Block Purge</t>
+          <t>Thanh Trừng Khối</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Trên Trời Dưới Đất Chỉ Có Đường Này Khó Đi Nhất</t>
+          <t>Suốt Càn Khôn Này Chỉ Có Một Con Đường Gian Nan Nhất</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Vũ Công Trên Đường Đua</t>
+          <t>Vũ công trên đường đua</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>On Every Road, Safety First</t>
+          <t>Trên Mọi Con Đường, An Toàn Là Trên Hết</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Tia Lấp Lánh và Sự Tò Mò</t>
+          <t>Tia Lấp Lánh Và Sự Tò Mò</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Nhảy Qua Aurora</t>
+          <t>Vượt Qua Cực Quang</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>A Rival Too Late</t>
+          <t>Đối Thủ Đến Quá Muộn</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Soliskin Free</t>
+          <t>Soliskin Tự Do</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Unrivaled</t>
+          <t>Vô địch</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Sao Các Người Lại Đuổi Theo Ta?</t>
+          <t>Tại sao ngươi lại đuổi theo ta?</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Người Cầm Gậy Là Ai?</t>
+          <t>Người Sử Dụng Thiết Bị Đầu Cuối, Là Ai?</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Winter's Mark</t>
+          <t>Dấu Ấn Mùa Đông</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Do Bạn Remember</t>
+          <t>Ngươi còn nhớ không?</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Used</t>
+          <t>Đã sử dụng</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Giai Đoạn 1 S1</t>
+          <t>Giai Đoạn 1 - S1</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14504,7 +14504,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14714,7 +14714,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Futures' Tithe</t>
+          <t>Cống Nạp Tương Lai</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14784,7 +14784,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Li Chanfei</t>
+          <t>Lý Chanfei</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Không xác định</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>Nữ</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Bong Bóng Hư Vô</t>
+          <t>Bong bóng Hư Vô</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Ge Xinyu</t>
+          <t>Cá Tâm Dư</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Origami Familiar</t>
+          <t>Linh Vật Origami</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Fortune Lot</t>
+          <t>Vé Số May Mắn</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Carving Kit Set</t>
+          <t>Bộ Dụng Cụ Khắc</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15834,7 +15834,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>"Trickster"</t>
+          <t>"Kẻ Lừa Đảo"</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Startorch Memory Album</t>
+          <t>Bộ Sưu Tập Ký Ức Sao Chổi</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>"Dream Maker"</t>
+          <t>"Người Tạo Giấc Mơ"</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Words Left Unsaid</t>
+          <t>Lời Chưa Nói</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16114,7 +16114,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Sẽ Không Còn Ai Khác Nữa…</t>
+          <t>Sẽ Không Còn Một Ai Nữa...</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Snowed In</t>
+          <t>Bị Tuyết Chôn Vùi</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Vanished Honami</t>
+          <t>Honami đã biến mất</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Dù Đường Có Vô Tận</t>
+          <t>Dẫu Đường Đi Không Điểm Dừng</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>A Gift</t>
+          <t>Một Món Quà</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>A Wasteland</t>
+          <t>Vùng Đất Hoang Tàn</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16534,7 +16534,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>A Bright Light</t>
+          <t>Ánh Sáng Rực Rỡ</t>
         </is>
       </c>
       <c r="N230" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>A Mob</t>
+          <t>Đám Đông</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>A Lie</t>
+          <t>Một Điều Dối Trá</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Hiệp ước Ổn định</t>
+          <t>Hiệp Ước Ổn Định</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Singularity Expansion</t>
+          <t>Mở Rộng Điểm Kỳ Dị</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Templates</t>
+          <t>Mẫu</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Unlimited (Frame Generation)</t>
+          <t>Không giới hạn (Tạo khung hình)</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>60 FPS (Frame Generation)</t>
+          <t>60 FPS (Tạo Khung Hình)</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Morning Star</t>
+          <t>Sao Mai</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Trang Bị</t>
+          <t>Trang bị</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Đã trang bị phụ kiện</t>
+          <t>Đã trang bị Trang sức</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Đã gỡ phụ kiện</t>
+          <t>Đã tháo Trang sức</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Trang phục Accessory</t>
+          <t>Phụ Kiện Trang Phục</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Xem Trang phục</t>
+          <t>Xem Trang Phục</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Đạt 10.000 điểm trong Stability Accords để mở khóa</t>
+          <t>Đạt 10.000 điểm trong Hiệp Ước Ổn Định để mở khóa</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31094,7 +31094,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Hoàn thành Septimont 4 trong "Star Bouncing"</t>
+          <t>Hoàn thành Septimont 4 trong "Nhảy Sao"</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Hoàn thành SkyArk 4 trong "Star Bouncing"</t>
+          <t>Hoàn thành SkyArk 4 trong "Nhảy Sao"</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Nhận 500 2nd Anniversary Coins trong "Second Coming of Solaris: Collab Season"</t>
+          <t>Thu thập 500 Đồng Xu Kỷ Niệm 2 Năm trong "Solaris Trở Lại: Mùa Cộng Tác"</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Nhận 1.000 2nd Anniversary Coins trong "Second Coming of Solaris: Collab Season"</t>
+          <t>Nhận được 1.000 Xu Kỷ Niệm 2 Năm trong "Solaris Trở Lại: Mùa Cộng Tác".</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31374,7 +31374,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Tham gia và hoàn thành tổng cộng 2 trận trong "Cubie Derby: Championship"</t>
+          <t>Tham gia và hoàn thành tổng cộng 2 trận đấu trong "Cubie Derby: Championship".</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 4.000 Illusive Specimen trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
+          <t>Thu thập tổng cộng 4.000 Illusive Specimen trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 6.000 Illusive Specimen trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
+          <t>Thu thập tổng cộng 6.000 Illusive Specimen trong "Depths of Illusive Realm: Chromatic Fantasy"</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Bountiful Waves</t>
+          <t>Sóng Dạt Dào</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Storyline Resources</t>
+          <t>Tài Nguyên Cốt Truyện</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Environment Resources</t>
+          <t>Tài Nguyên Môi Trường</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Storyline Resources</t>
+          <t>Tài Nguyên Cốt Truyện</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Environment Resources</t>
+          <t>Tài Nguyên Môi Trường</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Past Storyline Resources</t>
+          <t>Tài nguyên cốt truyện quá khứ</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Chính "Gold Suspended in Shadows" để có trải nghiệm tốt hơn</t>
+          <t>Hoàn thành Nhiệm vụ Chính "Vàng Pha Bóng Tối" để có trải nghiệm tốt hơn</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Kiểm tra Altar of Radiance</t>
+          <t>Kiểm tra Bàn Thờ Ánh Sáng</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Đến tháp ở Mournfell Canyon</t>
+          <t>Đến tháp ở Hẻm Núi Mournfell</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Đến tàn tích ở Border Mountains</t>
+          <t>Đến tàn tích trên dãy Border Mountains</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Đến Roya Frostlands</t>
+          <t>Đến vùng đất băng giá Roya Frostlands.</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Đến Twilight Woodlands</t>
+          <t>Đến Twilight Woodlands.</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Xây dựng lại Submerged Tunnel</t>
+          <t>Khôi phục Đường hầm Ngập nước</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32914,7 +32914,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Hoàn thành Spacetrek Observatory: Overwatch Giai đoạn</t>
+          <t>Hoàn thành Giai Đoạn Giám Sát tại Đài Thiên Văn Spacetrek</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32984,7 +32984,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Xây dựng lại Submerged Tunnel</t>
+          <t>Khôi phục Đường hầm Ngập nước</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Complete "What Burns Beneath Frostlands"</t>
+          <t>Hoàn thành "Điều Gì Cháy Dưới Lãnh Nguyên"</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Nâng cấp trạm gốc lên Cấp III</t>
+          <t>Nâng cấp Trạm Cơ Bản lên Cấp III</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Nâng cấp trạm gốc lên Cấp V</t>
+          <t>Nâng cấp Trạm Cơ Bản lên Cấp V</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Nói chuyện với Chiến binh Bình tâm</t>
+          <t>Nói chuyện với Chiến Binh Bình Tâm</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Nói chuyện với nhân viên Bối rối</t>
+          <t>Nói chuyện với nhân viên đang sốt ruột</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Space Cleared</t>
+          <t>Khu vực đã được dọn sạch</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34314,7 +34314,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Expedition Motorbike Aerial Tactics Mô-đun</t>
+          <t>Mô-đun Chiến Thuật Bay Cao Xe Máy Thám Hiểm</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Budding Golden Bough</t>
+          <t>Cành Vàng Mới Nảy</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34454,7 +34454,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Paradise Regained</t>
+          <t>Thiên Đường Phục Hồi</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Thước đo Tò mò</t>
+          <t>Thước Đo Tò Mò</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Ánh sáng trong Bóng tối</t>
+          <t>Ánh Sáng Trong Bóng Tối</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Đôi cánh Vượt qua Mùa đông</t>
+          <t>Đôi Cánh Vượt Mùa Đông</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Bản ghi chuyến đi: Đội khảo sát Đồng bằng Dimmr 1 (Trích đoạn Một)</t>
+          <t>Bản ghi chuyến đi: Đội Khảo Sát Đồng Bằng Dimmr 1 (Trích đoạn 1)</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Bản ghi chuyến đi: Đội khảo sát Đồng bằng Dimmr 1 (Trích đoạn Hai)</t>
+          <t>Bản ghi chuyến đi: Đội Khảo Sát Đồng Bằng Dimmr 1 (Trích đoạn 2)</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Báo cáo về Tình hình Gần đây tại Khe nứt Bị phong ấn ở Đồng bằng Dimmr</t>
+          <t>Báo cáo Tình hình Gần đây tại Khe Nứt Bị Phong Ấn ở Dimmr Plains</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Lịch sử trò chuyện của Official Shashou Cafe (Trích đoạn)</t>
+          <t>Lịch Sử Trò Chuyện của Shashou Cafe (Trích Đoạn)</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Báo cáo Phân tích Khả năng Truy vết về Sự tích tụ Bất thường ở Khu vực Đồng bằng Dimmr</t>
+          <t>Báo cáo Phân tích Khả năng Truy vết Sự tích tụ Bất thường tại Khu vực Đồng bằng Dimmr</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Unknown Recording: Voidthirst Cradle</t>
+          <t>Bản ghi bí ẩn: Nôi Khát Vực</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Namipon Kisses</t>
+          <t>Hôn của Namipon</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Mua Gói đặc biệt WavesLine: Golden Coffee Ring để mở khóa</t>
+          <t>Mua Gói Đặc Biệt WavesLine: Nhẫn Cà Phê Vàng để mở khóa</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35294,7 +35294,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Nhận để mở khóa khung chat WavesLine</t>
+          <t>Nhận để mở khóa biểu tượng trò chuyện WavesLine</t>
         </is>
       </c>
       <c r="N498" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Sweet Coffee Time</t>
+          <t>Giờ Cà Phê Ngọt Ngào</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Mua Gói Đặc Biệt WavesLine: Golden Coffee Ring để mở khóa</t>
+          <t>Mua Gói Đặc Biệt WavesLine: Nhẫn Cà Phê Vàng để mở khóa</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Nhận để mở khóa nền trò chuyện WavesLine</t>
+          <t>Lấy để mở khóa nền trò chuyện WavesLine</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
